--- a/resources/stimuliLexTALE.xlsx
+++ b/resources/stimuliLexTALE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marie\Desktop\Experiment Semantiek Pragmatiek\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medej\Desktop\scalar-implicatures\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EB8BFF-ECD5-4949-8559-DEF8D400CBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473DE4ED-B579-4E33-9B37-5D71EF3971FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -345,7 +345,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
